--- a/Compititor's_Price/Rockwool_Prices/Rockwool_Prices_11-08-2025.xlsx
+++ b/Compititor's_Price/Rockwool_Prices/Rockwool_Prices_11-08-2025.xlsx
@@ -485,34 +485,8 @@
       <c r="E2" t="n">
         <v>959.76</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: 
-Stacktrace:
-	GetHandleVerifier [0x0xe4fd23+62915]
-	GetHandleVerifier [0x0xe4fd64+62980]
-	(No symbol) [0x0xc83e13]
-	(No symbol) [0x0xccc89e]
-	(No symbol) [0x0xcccc3b]
-	(No symbol) [0x0xd14ec2]
-	(No symbol) [0x0xcf1424]
-	(No symbol) [0x0xd126ea]
-	(No symbol) [0x0xcf11d6]
-	(No symbol) [0x0xcc0833]
-	(No symbol) [0x0xcc16a4]
-	GetHandleVerifier [0x0x10b8d13+2590131]
-	GetHandleVerifier [0x0x10b3f5a+2570234]
-	GetHandleVerifier [0x0xe759da+217722]
-	GetHandleVerifier [0x0xe66048+153832]
-	GetHandleVerifier [0x0xe6c4ad+179533]
-	GetHandleVerifier [0x0xe57728+94152]
-	GetHandleVerifier [0x0xe578b2+94546]
-	GetHandleVerifier [0x0xe42bca+9322]
-	BaseThreadInitThunk [0x0x75d55d49+25]
-	RtlInitializeExceptionChain [0x0x771bd1ab+107]
-	RtlGetAppContainerNamedObjectPath [0x0x771bd131+561]
-</t>
-        </is>
+      <c r="F2" t="n">
+        <v>1124.28</v>
       </c>
       <c r="G2" t="n">
         <v>1020</v>
@@ -538,34 +512,8 @@
       <c r="E3" t="n">
         <v>79.98</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: 
-Stacktrace:
-	GetHandleVerifier [0x0xe4fd23+62915]
-	GetHandleVerifier [0x0xe4fd64+62980]
-	(No symbol) [0x0xc83e13]
-	(No symbol) [0x0xccc89e]
-	(No symbol) [0x0xcccc3b]
-	(No symbol) [0x0xd14ec2]
-	(No symbol) [0x0xcf1424]
-	(No symbol) [0x0xd126ea]
-	(No symbol) [0x0xcf11d6]
-	(No symbol) [0x0xcc0833]
-	(No symbol) [0x0xcc16a4]
-	GetHandleVerifier [0x0x10b8d13+2590131]
-	GetHandleVerifier [0x0x10b3f5a+2570234]
-	GetHandleVerifier [0x0xe759da+217722]
-	GetHandleVerifier [0x0xe66048+153832]
-	GetHandleVerifier [0x0xe6c4ad+179533]
-	GetHandleVerifier [0x0xe57728+94152]
-	GetHandleVerifier [0x0xe578b2+94546]
-	GetHandleVerifier [0x0xe42bca+9322]
-	BaseThreadInitThunk [0x0x75d55d49+25]
-	RtlInitializeExceptionChain [0x0x771bd1ab+107]
-	RtlGetAppContainerNamedObjectPath [0x0x771bd131+561]
-</t>
-        </is>
+      <c r="F3" t="n">
+        <v>93.69</v>
       </c>
       <c r="G3" t="n">
         <v>85</v>
@@ -933,34 +881,8 @@
       <c r="E14" t="n">
         <v>1031.76</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: 
-Stacktrace:
-	GetHandleVerifier [0x0xe4fd23+62915]
-	GetHandleVerifier [0x0xe4fd64+62980]
-	(No symbol) [0x0xc83e13]
-	(No symbol) [0x0xccc89e]
-	(No symbol) [0x0xcccc3b]
-	(No symbol) [0x0xd14ec2]
-	(No symbol) [0x0xcf1424]
-	(No symbol) [0x0xd126ea]
-	(No symbol) [0x0xcf11d6]
-	(No symbol) [0x0xcc0833]
-	(No symbol) [0x0xcc16a4]
-	GetHandleVerifier [0x0x10b8d13+2590131]
-	GetHandleVerifier [0x0x10b3f5a+2570234]
-	GetHandleVerifier [0x0xe759da+217722]
-	GetHandleVerifier [0x0xe66048+153832]
-	GetHandleVerifier [0x0xe6c4ad+179533]
-	GetHandleVerifier [0x0xe57728+94152]
-	GetHandleVerifier [0x0xe578b2+94546]
-	GetHandleVerifier [0x0xe42bca+9322]
-	BaseThreadInitThunk [0x0x75d55d49+25]
-	RtlInitializeExceptionChain [0x0x771bd1ab+107]
-	RtlGetAppContainerNamedObjectPath [0x0x771bd131+561]
-</t>
-        </is>
+      <c r="F14" t="n">
+        <v>1127.88</v>
       </c>
       <c r="G14" t="n">
         <v>907.92</v>
@@ -986,34 +908,8 @@
       <c r="E15" t="n">
         <v>85.98</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: 
-Stacktrace:
-	GetHandleVerifier [0x0xe4fd23+62915]
-	GetHandleVerifier [0x0xe4fd64+62980]
-	(No symbol) [0x0xc83e13]
-	(No symbol) [0x0xccc89e]
-	(No symbol) [0x0xcccc3b]
-	(No symbol) [0x0xd14ec2]
-	(No symbol) [0x0xcf1424]
-	(No symbol) [0x0xd126ea]
-	(No symbol) [0x0xcf11d6]
-	(No symbol) [0x0xcc0833]
-	(No symbol) [0x0xcc16a4]
-	GetHandleVerifier [0x0x10b8d13+2590131]
-	GetHandleVerifier [0x0x10b3f5a+2570234]
-	GetHandleVerifier [0x0xe759da+217722]
-	GetHandleVerifier [0x0xe66048+153832]
-	GetHandleVerifier [0x0xe6c4ad+179533]
-	GetHandleVerifier [0x0xe57728+94152]
-	GetHandleVerifier [0x0xe578b2+94546]
-	GetHandleVerifier [0x0xe42bca+9322]
-	BaseThreadInitThunk [0x0x75d55d49+25]
-	RtlInitializeExceptionChain [0x0x771bd1ab+107]
-	RtlGetAppContainerNamedObjectPath [0x0x771bd131+561]
-</t>
-        </is>
+      <c r="F15" t="n">
+        <v>93.98999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>75.66</v>
@@ -1041,34 +937,8 @@
       <c r="E16" t="n">
         <v>1079.76</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: 
-Stacktrace:
-	GetHandleVerifier [0x0xe4fd23+62915]
-	GetHandleVerifier [0x0xe4fd64+62980]
-	(No symbol) [0x0xc83e13]
-	(No symbol) [0x0xccc89e]
-	(No symbol) [0x0xcccc3b]
-	(No symbol) [0x0xd14ec2]
-	(No symbol) [0x0xcf1424]
-	(No symbol) [0x0xd126ea]
-	(No symbol) [0x0xcf11d6]
-	(No symbol) [0x0xcc0833]
-	(No symbol) [0x0xcc16a4]
-	GetHandleVerifier [0x0x10b8d13+2590131]
-	GetHandleVerifier [0x0x10b3f5a+2570234]
-	GetHandleVerifier [0x0xe759da+217722]
-	GetHandleVerifier [0x0xe66048+153832]
-	GetHandleVerifier [0x0xe6c4ad+179533]
-	GetHandleVerifier [0x0xe57728+94152]
-	GetHandleVerifier [0x0xe578b2+94546]
-	GetHandleVerifier [0x0xe42bca+9322]
-	BaseThreadInitThunk [0x0x75d55d49+25]
-	RtlInitializeExceptionChain [0x0x771bd1ab+107]
-	RtlGetAppContainerNamedObjectPath [0x0x771bd131+561]
-</t>
-        </is>
+      <c r="F16" t="n">
+        <v>1019.88</v>
       </c>
       <c r="G16" t="n">
         <v>1315.18</v>
@@ -1096,34 +966,8 @@
       <c r="E17" t="n">
         <v>89.98</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: 
-Stacktrace:
-	GetHandleVerifier [0x0xe4fd23+62915]
-	GetHandleVerifier [0x0xe4fd64+62980]
-	(No symbol) [0x0xc83e13]
-	(No symbol) [0x0xccc89e]
-	(No symbol) [0x0xcccc3b]
-	(No symbol) [0x0xd14ec2]
-	(No symbol) [0x0xcf1424]
-	(No symbol) [0x0xd126ea]
-	(No symbol) [0x0xcf11d6]
-	(No symbol) [0x0xcc0833]
-	(No symbol) [0x0xcc16a4]
-	GetHandleVerifier [0x0x10b8d13+2590131]
-	GetHandleVerifier [0x0x10b3f5a+2570234]
-	GetHandleVerifier [0x0xe759da+217722]
-	GetHandleVerifier [0x0xe66048+153832]
-	GetHandleVerifier [0x0xe6c4ad+179533]
-	GetHandleVerifier [0x0xe57728+94152]
-	GetHandleVerifier [0x0xe578b2+94546]
-	GetHandleVerifier [0x0xe42bca+9322]
-	BaseThreadInitThunk [0x0x75d55d49+25]
-	RtlInitializeExceptionChain [0x0x771bd1ab+107]
-	RtlGetAppContainerNamedObjectPath [0x0x771bd131+561]
-</t>
-        </is>
+      <c r="F17" t="n">
+        <v>84.98999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>109.6</v>
@@ -1184,36 +1028,10 @@
         <v>1299</v>
       </c>
       <c r="E19" t="n">
-        <v>959.76</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: 
-Stacktrace:
-	GetHandleVerifier [0x0xe4fd23+62915]
-	GetHandleVerifier [0x0xe4fd64+62980]
-	(No symbol) [0x0xc83e13]
-	(No symbol) [0x0xccc89e]
-	(No symbol) [0x0xcccc3b]
-	(No symbol) [0x0xd14ec2]
-	(No symbol) [0x0xcf1424]
-	(No symbol) [0x0xd126ea]
-	(No symbol) [0x0xcf11d6]
-	(No symbol) [0x0xcc0833]
-	(No symbol) [0x0xcc16a4]
-	GetHandleVerifier [0x0x10b8d13+2590131]
-	GetHandleVerifier [0x0x10b3f5a+2570234]
-	GetHandleVerifier [0x0xe759da+217722]
-	GetHandleVerifier [0x0xe66048+153832]
-	GetHandleVerifier [0x0xe6c4ad+179533]
-	GetHandleVerifier [0x0xe57728+94152]
-	GetHandleVerifier [0x0xe578b2+94546]
-	GetHandleVerifier [0x0xe42bca+9322]
-	BaseThreadInitThunk [0x0x75d55d49+25]
-	RtlInitializeExceptionChain [0x0x771bd1ab+107]
-	RtlGetAppContainerNamedObjectPath [0x0x771bd131+561]
-</t>
-        </is>
+        <v>937.4400000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1067.88</v>
       </c>
       <c r="G19" t="n">
         <v>1070.64</v>
@@ -1237,36 +1055,10 @@
         <v>108.25</v>
       </c>
       <c r="E20" t="n">
-        <v>79.98</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: 
-Stacktrace:
-	GetHandleVerifier [0x0xe4fd23+62915]
-	GetHandleVerifier [0x0xe4fd64+62980]
-	(No symbol) [0x0xc83e13]
-	(No symbol) [0x0xccc89e]
-	(No symbol) [0x0xcccc3b]
-	(No symbol) [0x0xd14ec2]
-	(No symbol) [0x0xcf1424]
-	(No symbol) [0x0xd126ea]
-	(No symbol) [0x0xcf11d6]
-	(No symbol) [0x0xcc0833]
-	(No symbol) [0x0xcc16a4]
-	GetHandleVerifier [0x0x10b8d13+2590131]
-	GetHandleVerifier [0x0x10b3f5a+2570234]
-	GetHandleVerifier [0x0xe759da+217722]
-	GetHandleVerifier [0x0xe66048+153832]
-	GetHandleVerifier [0x0xe6c4ad+179533]
-	GetHandleVerifier [0x0xe57728+94152]
-	GetHandleVerifier [0x0xe578b2+94546]
-	GetHandleVerifier [0x0xe42bca+9322]
-	BaseThreadInitThunk [0x0x75d55d49+25]
-	RtlInitializeExceptionChain [0x0x771bd1ab+107]
-	RtlGetAppContainerNamedObjectPath [0x0x771bd131+561]
-</t>
-        </is>
+        <v>78.12</v>
+      </c>
+      <c r="F20" t="n">
+        <v>88.98999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>89.22</v>
@@ -1294,34 +1086,8 @@
       <c r="E21" t="n">
         <v>1050.6</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: 
-Stacktrace:
-	GetHandleVerifier [0x0xe4fd23+62915]
-	GetHandleVerifier [0x0xe4fd64+62980]
-	(No symbol) [0x0xc83e13]
-	(No symbol) [0x0xccc89e]
-	(No symbol) [0x0xcccc3b]
-	(No symbol) [0x0xd14ec2]
-	(No symbol) [0x0xcf1424]
-	(No symbol) [0x0xd126ea]
-	(No symbol) [0x0xcf11d6]
-	(No symbol) [0x0xcc0833]
-	(No symbol) [0x0xcc16a4]
-	GetHandleVerifier [0x0x10b8d13+2590131]
-	GetHandleVerifier [0x0x10b3f5a+2570234]
-	GetHandleVerifier [0x0xe759da+217722]
-	GetHandleVerifier [0x0xe66048+153832]
-	GetHandleVerifier [0x0xe6c4ad+179533]
-	GetHandleVerifier [0x0xe57728+94152]
-	GetHandleVerifier [0x0xe578b2+94546]
-	GetHandleVerifier [0x0xe42bca+9322]
-	BaseThreadInitThunk [0x0x75d55d49+25]
-	RtlInitializeExceptionChain [0x0x771bd1ab+107]
-	RtlGetAppContainerNamedObjectPath [0x0x771bd131+561]
-</t>
-        </is>
+      <c r="F21" t="n">
+        <v>1097.88</v>
       </c>
       <c r="G21" t="n">
         <v>1096.56</v>
@@ -1349,34 +1115,8 @@
       <c r="E22" t="n">
         <v>87.55</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: 
-Stacktrace:
-	GetHandleVerifier [0x0xe4fd23+62915]
-	GetHandleVerifier [0x0xe4fd64+62980]
-	(No symbol) [0x0xc83e13]
-	(No symbol) [0x0xccc89e]
-	(No symbol) [0x0xcccc3b]
-	(No symbol) [0x0xd14ec2]
-	(No symbol) [0x0xcf1424]
-	(No symbol) [0x0xd126ea]
-	(No symbol) [0x0xcf11d6]
-	(No symbol) [0x0xcc0833]
-	(No symbol) [0x0xcc16a4]
-	GetHandleVerifier [0x0x10b8d13+2590131]
-	GetHandleVerifier [0x0x10b3f5a+2570234]
-	GetHandleVerifier [0x0xe759da+217722]
-	GetHandleVerifier [0x0xe66048+153832]
-	GetHandleVerifier [0x0xe6c4ad+179533]
-	GetHandleVerifier [0x0xe57728+94152]
-	GetHandleVerifier [0x0xe578b2+94546]
-	GetHandleVerifier [0x0xe42bca+9322]
-	BaseThreadInitThunk [0x0x75d55d49+25]
-	RtlInitializeExceptionChain [0x0x771bd1ab+107]
-	RtlGetAppContainerNamedObjectPath [0x0x771bd131+561]
-</t>
-        </is>
+      <c r="F22" t="n">
+        <v>91.48999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>91.38</v>
@@ -3740,34 +3480,8 @@
       <c r="E87" t="n">
         <v>79.98</v>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: 
-Stacktrace:
-	GetHandleVerifier [0x0xe4fd23+62915]
-	GetHandleVerifier [0x0xe4fd64+62980]
-	(No symbol) [0x0xc83e13]
-	(No symbol) [0x0xccc89e]
-	(No symbol) [0x0xcccc3b]
-	(No symbol) [0x0xd14ec2]
-	(No symbol) [0x0xcf1424]
-	(No symbol) [0x0xd126ea]
-	(No symbol) [0x0xcf11d6]
-	(No symbol) [0x0xcc0833]
-	(No symbol) [0x0xcc16a4]
-	GetHandleVerifier [0x0x10b8d13+2590131]
-	GetHandleVerifier [0x0x10b3f5a+2570234]
-	GetHandleVerifier [0x0xe759da+217722]
-	GetHandleVerifier [0x0xe66048+153832]
-	GetHandleVerifier [0x0xe6c4ad+179533]
-	GetHandleVerifier [0x0xe57728+94152]
-	GetHandleVerifier [0x0xe578b2+94546]
-	GetHandleVerifier [0x0xe42bca+9322]
-	BaseThreadInitThunk [0x0x75d55d49+25]
-	RtlInitializeExceptionChain [0x0x771bd1ab+107]
-	RtlGetAppContainerNamedObjectPath [0x0x771bd131+561]
-</t>
-        </is>
+      <c r="F87" t="n">
+        <v>88.98999999999999</v>
       </c>
       <c r="G87" t="n">
         <v>89.64</v>
